--- a/outputs/AR_Final.xlsx
+++ b/outputs/AR_Final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/daniellieskovsky/Desktop/diplomova_praca/outputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D4FC96A-B9C6-E54D-8342-AB45E6FD94E3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93ED0E9F-363A-1B42-B486-10068A569496}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="question_map" sheetId="1" r:id="rId1"/>
@@ -1108,6 +1108,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="80.83203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -1525,6 +1528,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="220.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -2516,6 +2522,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="54.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="171.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -2845,6 +2857,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="54" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="182" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -3174,6 +3190,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="54" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="168.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -3503,6 +3524,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="54" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="219.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -3876,6 +3902,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="54.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -4205,6 +4234,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="54.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="199.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
